--- a/data/outputs/diagnostico_matcheo.xlsx
+++ b/data/outputs/diagnostico_matcheo.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-26 11:55:55</t>
+          <t>2026-03-27 16:49:56</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Permisos de Embarque MOA Reingenieria</t>
+          <t>Permisos de Embarque MOA Reingeniería</t>
         </is>
       </c>
       <c r="C16" t="b">

--- a/data/outputs/diagnostico_matcheo.xlsx
+++ b/data/outputs/diagnostico_matcheo.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-27 16:49:56</t>
+          <t>2026-04-10 18:50:53</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30881</v>
+        <v>39216</v>
       </c>
     </row>
     <row r="4">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17220</v>
+        <v>19616</v>
       </c>
     </row>
     <row r="7">
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28285</v>
+        <v>36381</v>
       </c>
     </row>
     <row r="9">
@@ -518,7 +518,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>92.8%</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2261</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="11">
@@ -540,7 +540,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>377</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13659</v>
+        <v>19223</v>
       </c>
       <c r="C3" t="n">
-        <v>44.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17220</v>
+        <v>19616</v>
       </c>
       <c r="C4" t="n">
-        <v>55.8</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9334</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3744</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1655</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="5">
@@ -697,67 +697,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>727</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CARGA DDJJ - F2668</t>
+          <t>GUI: Instalación</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GUI: Instalación</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Profesional</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Profesional</t>
+          <t>GUI: Control Correlatividad</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GUI: Control Correlatividad</t>
+          <t>GUI: Identificación Duplicados</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GUI: Identificación Duplicados</t>
+          <t>GUI: Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GUI: Descarga de Deducciones Sufridas</t>
+          <t>CARGA DDJJ - F2668</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -767,17 +767,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ACROBAT TOOLS</t>
+          <t>GUI: Conciliación Deducciones (ERP vs Fisco Nac &amp; Prov)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -787,17 +787,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GUI: Conciliación Deducciones (ERP vs Fisco Nac &amp; Prov)</t>
+          <t>ACROBAT TOOLS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -813,51 +813,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GUI: Controlar Totales</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
+          <t>GUI: Controlar Totales</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GUI: Sumarización &amp; Control por Totales</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Descarga de Deducciones Sufridas</t>
+          <t>GUI: Sumarización &amp; Control por Totales</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -893,7 +893,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>GUI: Control Registros Faltantes</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -903,61 +903,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GUI: Control Registros Faltantes</t>
+          <t>GUI:  Detección de duplicados</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GUI:  Detección de duplicados</t>
+          <t>GUI: Control Percepciones</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GUI: Control Percepciones</t>
+          <t>GUI: Controlar correlatividad</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GUI: Controlar correlatividad</t>
+          <t>GUI: Control de Percepciones Sufridas</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GUI: Control de Percepciones Sufridas</t>
+          <t>AFIP voucher correlativity control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFIP voucher correlativity control</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9633</v>
+        <v>12574</v>
       </c>
     </row>
     <row r="3">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6781</v>
+        <v>9042</v>
       </c>
     </row>
     <row r="4">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2517</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="5">
@@ -1048,37 +1048,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>274</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GUI: Instalación</t>
+          <t>UY - Envio Recibo de sueldos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GUI: Instalacion</t>
+          <t>UY - Envio Recibo de Sueldos</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>228</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UY - Envio Recibo de sueldos</t>
+          <t>GUI: Instalación</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UY - Envio Recibo de Sueldos</t>
+          <t>GUI: Instalacion</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>202</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8">
@@ -1108,127 +1108,127 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
+          <t>MX - Ultragenyx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>MX - Ultragenyx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Payroll - Match recibo CUIL en PDF</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Payroll - Match Recibo CUIL</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MX - Ultragenyx</t>
+          <t>CO - Ultragenyx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MX - Ultragenyx</t>
+          <t>CO - Ultragenyx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F572</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F572</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
+          <t>Payroll - Match recibo CUIL en PDF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>Payroll - Match Recibo CUIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CO - Ultragenyx</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CO - Ultragenyx</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1454</v>
+        <v>1757</v>
       </c>
       <c r="C2" t="n">
-        <v>1454</v>
+        <v>1757</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1155</v>
+        <v>1568</v>
       </c>
       <c r="C3" t="n">
-        <v>1155</v>
+        <v>1568</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>860</v>
+        <v>969</v>
       </c>
       <c r="C4" t="n">
-        <v>859</v>
+        <v>968</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1362,39 +1362,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIMPLOT ARGENTINA S.R.L</t>
+          <t>TERNIUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="C5" t="n">
-        <v>458</v>
+        <v>529</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>96.59999999999999</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERNIUM</t>
+          <t>SIMPLOT ARGENTINA S.R.L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>99.8</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1419,39 +1419,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EDGE ARGENTINA S.R.L</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="C8" t="n">
-        <v>232</v>
+        <v>437</v>
       </c>
       <c r="D8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>EDGE ARGENTINA S.R.L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>367</v>
+        <v>406</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="10">
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="C11" t="n">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1499,162 +1499,162 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="C12" t="n">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>92.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ADIDAS ARGENTINA S.A - ARCA</t>
+          <t>GUERRERO CERON, CRISTIAN ALEJANDRO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="C13" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CYANAMID DE ARGENTINA S A SUC BS AS</t>
+          <t>ADIDAS ARGENTINA S.A - ARCA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C14" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>96.3</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES ARG. S.A</t>
+          <t>CYANAMID DE ARGENTINA S A SUC BS AS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C15" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>91.59999999999999</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MAGNETI MARELLI CONJ.DE ESCAPE S.A</t>
+          <t>J&amp;J</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C16" t="n">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>90.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PFIZER S.R.L - PROVINCIALES</t>
+          <t>ABBOTT LABORATORIES ARG. S.A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C17" t="n">
-        <v>104</v>
+        <v>217</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J&amp;J</t>
+          <t>MAGNETI MARELLI CONJ.DE ESCAPE S.A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C18" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>98.59999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAGNETI MARELLI REPUESTOS S.A</t>
+          <t>PFIZER S.R.L - PROVINCIALES</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="C19" t="n">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="E19" t="n">
-        <v>88.40000000000001</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PFIZER S.R.L - SICNEA</t>
+          <t>F.Tacuarembo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="C20" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1666,33 +1666,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VENTURA PEÑA, MIGUEL ANGEL</t>
+          <t>MAGNETI MARELLI REPUESTOS S.A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C21" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GUERRERO CERON, CRISTIAN ALEJANDRO</t>
+          <t>VENTURA PEÑA, MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C22" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1704,71 +1704,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JANSSEN CILAG FARMACEUTICA S.A</t>
+          <t>PFIZER S.R.L - SICNEA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C23" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>83.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JOHNSON &amp; JOHNSON MEDICAL S.A</t>
+          <t>KONIG ERGAS, YAEL CECILIA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NATURA COSMETICOS S.A</t>
+          <t>DA ROCHA PADILHA SIMOES CUNHA, LISE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>66.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RAMOS VALENZUELA, LUCAS ALEJANDRO</t>
+          <t>SIMOES DA CUNHA, MARCUS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C26" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1780,33 +1780,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PFIZER S.R.L - ARCA</t>
+          <t>SIMOES DA CUNHA, MARIA CLARA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C27" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RODRIGUES SILVEIRA, BRUNA</t>
+          <t>HUACANI MAMANI, GABRIEL ALDEMAR</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="C28" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1818,90 +1818,90 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LUIZ NUNES DA SILVA, RONDINELLI</t>
+          <t>JANSSEN CILAG FARMACEUTICA S.A</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C29" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>F.Tacuarembo</t>
+          <t>JOHNSON &amp; JOHNSON MEDICAL S.A</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="C30" t="n">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ROBERTS, JOHN ALEXANDER</t>
+          <t>NATURA COSMETICOS S.A</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C31" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ABBVIE S.A</t>
+          <t>RAMOS VALENZUELA, LUCAS ALEJANDRO</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>138</v>
+      </c>
+      <c r="C32" t="n">
+        <v>138</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
         <v>100</v>
-      </c>
-      <c r="C32" t="n">
-        <v>45</v>
-      </c>
-      <c r="D32" t="n">
-        <v>48</v>
-      </c>
-      <c r="E32" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MARTINS ALVES, CAROLINE</t>
+          <t>LA RURAL S.A</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="C33" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1913,33 +1913,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADIDAS ARGENTINA S.A - PROVINCIALES</t>
+          <t>PFIZER S.R.L - ARCA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="C34" t="n">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>87.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BLANC LUJAMBIO, PATRICIA ARACELI</t>
+          <t>VELARDE ALARCON, CHRISTIAN ANDRES</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C35" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1951,14 +1951,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TaxTech</t>
+          <t>RODRIGUES SILVEIRA, BRUNA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C36" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1970,14 +1970,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>LUIZ NUNES DA SILVA, RONDINELLI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C37" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1989,14 +1989,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ROCHE</t>
+          <t>BUMERAN. COM ARGENTINA S.A.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C38" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2008,14 +2008,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEWMONT</t>
+          <t>ROCHE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="C39" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2027,14 +2027,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EXPEDITORS</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C40" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2046,14 +2046,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALVES, EMERSON LUCIANO</t>
+          <t>ROBERTS, JOHN ALEXANDER</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C41" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2065,33 +2065,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ARROYO REVATTA, LUISA VERONICA</t>
+          <t>ABBVIE S.A</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>MARTINS ALVES, CAROLINE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C43" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2103,14 +2103,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MUNIZ MASSA, JOAO</t>
+          <t>EXPEDITORS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C44" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2122,33 +2122,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TABOADA ROJAS, CHRISTOPHER MANUEL</t>
+          <t>ADIDAS ARGENTINA S.A - PROVINCIALES</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2160,14 +2160,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LDS</t>
+          <t>Cabify S.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2179,14 +2179,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRUPO NAVENT S.R.L.</t>
+          <t>BLANC LUJAMBIO, PATRICIA ARACELI</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2198,14 +2198,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>FMC TECHNOLOGIES ARGENTINA S.R.L.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C49" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2217,14 +2217,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MARTINS ALVES, SANDRA</t>
+          <t>TaxTech</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C50" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2236,14 +2236,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>EQUINOR ARGENTINA S.A.U.</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C51" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9633</v>
+        <v>12574</v>
       </c>
       <c r="E2" t="n">
-        <v>9633</v>
+        <v>12574</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6781</v>
+        <v>9042</v>
       </c>
       <c r="E3" t="n">
-        <v>6781</v>
+        <v>9042</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2360,109 +2360,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>GUI: Padrones Impositivos (Nac &amp; Prov)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Padrones Impositivos - ComplyPro</t>
         </is>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4500</v>
+        <v>4576</v>
       </c>
       <c r="E4" t="n">
-        <v>3750</v>
+        <v>4333</v>
       </c>
       <c r="F4" t="n">
-        <v>688</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>83.3</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GUI: Padrones Impositivos (Nac &amp; Prov)</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Padrones Impositivos - ComplyPro</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3744</v>
+        <v>4500</v>
       </c>
       <c r="E5" t="n">
-        <v>3579</v>
+        <v>3750</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="G5" t="n">
-        <v>95.59999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Tracking de Vencimientos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report - Precios de Transferencia</t>
+          <t>Calendarios Impositivos</t>
         </is>
       </c>
       <c r="C6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2517</v>
+        <v>2986</v>
       </c>
       <c r="E6" t="n">
-        <v>1177</v>
+        <v>2969</v>
       </c>
       <c r="F6" t="n">
-        <v>1244</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>46.8</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tracking de Vencimientos</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calendarios Impositivos</t>
+          <t>Tablas Ratio Report - Precios de Transferencia</t>
         </is>
       </c>
       <c r="C7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1501</v>
+        <v>2672</v>
       </c>
       <c r="E7" t="n">
-        <v>1499</v>
+        <v>1296</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1280</v>
       </c>
       <c r="G7" t="n">
-        <v>99.90000000000001</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="8">
@@ -2480,70 +2480,70 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>274</v>
+        <v>454</v>
       </c>
       <c r="E8" t="n">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="F8" t="n">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GUI: Instalación</t>
+          <t>UY - Envio Recibo de sueldos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GUI: Instalacion</t>
+          <t>UY - Envio Recibo de Sueldos</t>
         </is>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>228</v>
+        <v>375</v>
       </c>
       <c r="E9" t="n">
-        <v>211</v>
+        <v>373</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>92.5</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UY - Envio Recibo de sueldos</t>
+          <t>GUI: Instalación</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UY - Envio Recibo de Sueldos</t>
+          <t>GUI: Instalacion</t>
         </is>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>99</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="11">
@@ -2603,49 +2603,49 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GUI: Identificación Duplicados</t>
+          <t>Permisos de Embarque</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Control de duplicados - ComplyPro</t>
+          <t>Permisos de Embarque MOA Reingeniería</t>
         </is>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GUI: Descarga de Deducciones Sufridas</t>
+          <t>GUI: Identificación Duplicados</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Descarga de deducciones - ComplyPro</t>
+          <t>Control de duplicados - ComplyPro</t>
         </is>
       </c>
       <c r="C14" t="b">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2657,82 +2657,82 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GUI: Identificación de registros faltantes</t>
+          <t>GUI: Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Identificacion de registros faltantes - ComplyPro</t>
+          <t>Descarga de deducciones - ComplyPro</t>
         </is>
       </c>
       <c r="C15" t="b">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Permisos de Embarque</t>
+          <t>GUI: Identificación de registros faltantes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Permisos de Embarque MOA Reingeniería</t>
+          <t>Identificacion de registros faltantes - ComplyPro</t>
         </is>
       </c>
       <c r="C16" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>43.8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ACROBAT TOOLS</t>
+          <t>GUI: Conciliación Deducciones (ERP vs Fisco Nac &amp; Prov)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acrobat Tools</t>
+          <t>Conciliacion de Deducciones - ComplyPro</t>
         </is>
       </c>
       <c r="C17" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E17" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -2750,415 +2750,415 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>92.59999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GUI: Conciliación Deducciones (ERP vs Fisco Nac &amp; Prov)</t>
+          <t>ACROBAT TOOLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Conciliacion de Deducciones - ComplyPro</t>
+          <t>Acrobat Tools</t>
         </is>
       </c>
       <c r="C19" t="b">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GUI: Detección de duplicados</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Control de duplicados - ComplyPro</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="C20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GUI: Controlar Totales</t>
+          <t>MX - Ultragenyx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sumarizacion y control por totales - ComplyPro</t>
+          <t>MX - Ultragenyx</t>
         </is>
       </c>
       <c r="C21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
+          <t>GUI: Detección de duplicados</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>Control de duplicados - ComplyPro</t>
         </is>
       </c>
       <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>59</v>
+      </c>
+      <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" t="n">
-        <v>41</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7</v>
-      </c>
       <c r="G22" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>91.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Payroll - Match recibo CUIL en PDF</t>
+          <t>CO - Ultragenyx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Payroll - Match Recibo CUIL</t>
+          <t>CO - Ultragenyx</t>
         </is>
       </c>
       <c r="C24" t="b">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MX - Ultragenyx</t>
+          <t>GUI: Controlar Totales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MX - Ultragenyx</t>
+          <t>Sumarizacion y control por totales - ComplyPro</t>
         </is>
       </c>
       <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>53</v>
+      </c>
+      <c r="E25" t="n">
+        <v>53</v>
+      </c>
+      <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="n">
-        <v>40</v>
-      </c>
-      <c r="E25" t="n">
-        <v>38</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Descarga de Deducciones Sufridas</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Descarga de deducciones - ComplyPro</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E26" t="n">
+        <v>41</v>
+      </c>
+      <c r="F26" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="n">
-        <v>32</v>
-      </c>
       <c r="G26" t="n">
-        <v>17.9</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GUI: Sumarización &amp; Control por Totales</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sumarizacion y control por totales - ComplyPro</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>94.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>F572</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F572</t>
+          <t>Descarga de deducciones - ComplyPro</t>
         </is>
       </c>
       <c r="C28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>Payroll - Match recibo CUIL en PDF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>Payroll - Match Recibo CUIL</t>
         </is>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>32.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
+          <t>GUI: Sumarización &amp; Control por Totales</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SLATAM - Validacion Tiempos</t>
+          <t>Sumarizacion y control por totales - ComplyPro</t>
         </is>
       </c>
       <c r="C30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>77.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CO - Ultragenyx</t>
+          <t>NFE UY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CO - Ultragenyx</t>
+          <t>NFE UY</t>
         </is>
       </c>
       <c r="C31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>92</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GUI: Control Totales</t>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sumarizacion y control por totales - ComplyPro</t>
+          <t>SLATAM - Validacion Tiempos</t>
         </is>
       </c>
       <c r="C32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GUI: Control Registros Faltantes</t>
+          <t>GUI: Control Totales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Identificacion de registros faltantes - ComplyPro</t>
+          <t>Sumarizacion y control por totales - ComplyPro</t>
         </is>
       </c>
       <c r="C33" t="b">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3170,22 +3170,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GUI:  Detección de duplicados</t>
+          <t>GUI: Control Registros Faltantes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Control de duplicados - ComplyPro</t>
+          <t>Identificacion de registros faltantes - ComplyPro</t>
         </is>
       </c>
       <c r="C34" t="b">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3197,22 +3197,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Revision de Domicilios Fiscales Electronicos</t>
+          <t>GUI:  Detección de duplicados</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Revision Domicilios Fiscales Electronicos</t>
+          <t>Control de duplicados - ComplyPro</t>
         </is>
       </c>
       <c r="C35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3224,22 +3224,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GUI: Control Percepciones</t>
+          <t>Revision de Domicilios Fiscales Electronicos</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Padrones Impositivos - ComplyPro</t>
+          <t>Revision Domicilios Fiscales Electronicos</t>
         </is>
       </c>
       <c r="C36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GUI: Controlar correlatividad</t>
+          <t>GUI: Control Percepciones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Control de correlatividad - ComplyPro</t>
+          <t>Padrones Impositivos - ComplyPro</t>
         </is>
       </c>
       <c r="C37" t="b">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GUI: Control de Percepciones Sufridas</t>
+          <t>GUI: Controlar correlatividad</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Padrones Impositivos - ComplyPro</t>
+          <t>Control de correlatividad - ComplyPro</t>
         </is>
       </c>
       <c r="C38" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AFIP voucher correlativity control</t>
+          <t>GUI: Control de Percepciones Sufridas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Control de correlatividad - ComplyPro</t>
+          <t>Padrones Impositivos - ComplyPro</t>
         </is>
       </c>
       <c r="C39" t="b">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3344,16 +3344,151 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GUI: Detector de Duplicados</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GUI: Detector de Duplicados</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GUI: Detector de Registros Faltantes</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GUI: Detector de Registros Faltantes</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BMRN - Certificados de retención</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BMRN - Certificados de retención</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AFIP voucher correlativity control</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Control de correlatividad - ComplyPro</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SygnOff</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SygnOff</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3367,7 +3502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3395,7 +3530,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>775</v>
+        <v>811</v>
       </c>
     </row>
     <row r="3">
@@ -3436,7 +3571,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
@@ -3457,27 +3592,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GUI: Control Correlatividad</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ABBVIE S.A</t>
-        </is>
-      </c>
+          <t>GUI: Control Correlatividad</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -3488,11 +3619,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FACEBOOK ARGENTINA S.R.L</t>
+          <t>ABBVIE S.A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -3503,11 +3634,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NATURA COSMETICOS S.A</t>
+          <t>FACEBOOK ARGENTINA S.R.L</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -3518,48 +3649,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EUROP ASSISTANCE ARGENTINA S.A</t>
+          <t>NATURA COSMETICOS S.A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Permisos de Embarque</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>NFE Alert</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EUROP ASSISTANCE ARGENTINA S.A</t>
+        </is>
+      </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Descarga de Deducciones Sufridas</t>
+          <t>Permisos de Embarque</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JANSSEN CILAG FARMACEUTICA S.A</t>
-        </is>
-      </c>
+          <t>GUI: Instalación</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -3570,11 +3701,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES ARG. S.A</t>
+          <t>JANSSEN CILAG FARMACEUTICA S.A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -3600,11 +3731,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAGNETI MARELLI CONJ.DE ESCAPE S.A</t>
+          <t>ABBOTT LABORATORIES ARG. S.A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -3625,23 +3756,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>NFE Alert</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MAGNETI MARELLI CONJ.DE ESCAPE S.A</t>
+        </is>
+      </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GUI: Instalación</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -3652,16 +3787,20 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACROBAT TOOLS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Permisos de Embarque</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BUNGE</t>
+        </is>
+      </c>
       <c r="C22" t="n">
         <v>15</v>
       </c>
@@ -3669,46 +3808,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ULTRAGENYX</t>
-        </is>
-      </c>
+          <t>ACROBAT TOOLS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Tracking de Vencimientos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>,</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Emsa ROA - Errores ROA</t>
+          <t>ULTRAGENYX</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -3719,37 +3854,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>Emsa ROA - Errores ROA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SIMPLOT ARGENTINA S.R.L</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMSA ROA</t>
+          <t>SIMPLOT ARGENTINA S.R.L</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3764,22 +3899,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KODAK</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Profesional</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EMSA ROA</t>
+        </is>
+      </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -3790,7 +3929,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Copetro CAN</t>
+          <t>KODAK</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3820,41 +3959,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>Copetro CAN</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>TELCOSUR S.A</t>
-        </is>
-      </c>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Profesional</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allflex MO SNSS</t>
+          <t>TELCOSUR S.A</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3865,22 +4000,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COPETRO</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>CARGA DDJJ - F2668</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caso Testing 1 MATCH CODIGO ROA v3.7</t>
+          <t>amiriarte</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3890,10 +4025,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>NFE Alert</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ADIDAS ARGENTINA S.A - PROVINCIALES</t>
+        </is>
+      </c>
       <c r="C38" t="n">
         <v>7</v>
       </c>
@@ -3901,14 +4040,10 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ADIDAS ARGENTINA S.A - PROVINCIALES</t>
-        </is>
-      </c>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Socio</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>7</v>
       </c>
@@ -3921,127 +4056,123 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Copetro amiel</t>
+          <t>Caso Testing 1 MATCH CODIGO ROA v3.7</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CARGA DDJJ - F2668</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Allflex MO SNSS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COPETRO</t>
+        </is>
+      </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Permisos de Embarque</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HELMERICH</t>
+          <t>Raizen</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Permisos de Embarque</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Raizen</t>
+          <t>TELCOSUR S.A</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>CARGA DDJJ - F2668</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CITRU</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Permisos de Embarque</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NOURYON</t>
-        </is>
-      </c>
+          <t>GUI: Actualizacion</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Permisos de Embarque</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BUNGE</t>
-        </is>
-      </c>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Marketplace</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PFIZER S.R.L - ARCA</t>
+          <t>HELMERICH</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -4052,26 +4183,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EURODRIVE_ROA_CA0</t>
+          <t>Copetro amiel</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Permisos de Embarque</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Citrusvil ROA - Errores ROA</t>
+          <t>NOURYON</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -4082,11 +4213,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tetra MO</t>
+          <t>CITRU</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -4097,7 +4228,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EMSA_ROA_SAC</t>
+          <t>EURODRIVE_ROA_CA0</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4112,7 +4243,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INGREDION</t>
+          <t>Citrusvil ROA - Errores ROA</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4127,7 +4258,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Cistrusvil - Sin macro corrida</t>
+          <t>Tetra MO</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4137,12 +4268,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPOTIFY</t>
+          <t>Testing Cam - ROA Cistrusvil - Sin macro corrida</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4152,31 +4283,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMSA MB</t>
+          <t>PFIZER S.R.L - ARCA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Allflex Testing</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -4187,11 +4318,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ingredion MO</t>
+          <t>INGREDION</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -4202,11 +4333,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citrusvil MB</t>
+          <t>EMSA_ROA_SAC</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -4217,7 +4348,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RatioReport MATCH CODIGO ROA v3.7</t>
+          <t>Radio victoria ROA - con errores</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4232,7 +4363,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Radio Victoria ROA - Con errores</t>
+          <t>RatioReport MATCH CODIGO ROA v3.7</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4247,7 +4378,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Radio victoria ROA - con errores</t>
+          <t>Radio Victoria ROA - Con errores</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4257,10 +4388,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Macroanexo MB</t>
+        </is>
+      </c>
       <c r="C63" t="n">
         <v>3</v>
       </c>
@@ -4268,12 +4403,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>MX - Ultragenyx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citrusvil ROA - Casos con errores</t>
+          <t>ULTRAGENYX</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4283,12 +4418,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Citrusvil MO</t>
+          <t>J&amp;J</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4298,12 +4433,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>J&amp;J</t>
+          <t>test formal con el seÃ±or oven</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4318,7 +4453,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kodak ROA</t>
+          <t>Copetro MB</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -4333,7 +4468,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMSA - ROA Con Errores</t>
+          <t>Kodak ROA</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -4348,7 +4483,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Helmerich &amp; Payne ROA</t>
+          <t>Allflex Testing</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -4363,7 +4498,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>test formal con el seÃ±or oven</t>
+          <t>Macroanex MO</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4378,7 +4513,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ITT CAN</t>
+          <t>EMSA - ROA Con Errores</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4393,7 +4528,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Citrusvil</t>
+          <t>Citrusvil MO</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4408,7 +4543,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Macroanexo MB</t>
+          <t>EMSA MB</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4418,14 +4553,10 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Macroanex MO</t>
-        </is>
-      </c>
+          <t>Operaciones SLATAM &amp; Talento - Validacion de tiempos y utilizacion - Seun</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>3</v>
       </c>
@@ -4438,7 +4569,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Copetro MB</t>
+          <t>Helmerich &amp; Payne  ROA</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4448,16 +4579,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>UY - Envio Recibo de sueldos</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Coralnet</t>
+          <t>Citrusvil ROA - Casos con errores</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4468,11 +4599,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Renault - Sin macro corrida</t>
+          <t>ITT CAN</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4483,11 +4614,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA SEW - Sin macro corrida</t>
+          <t>Ingredion MO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4498,11 +4629,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sew Eurodrive ROA - con errores</t>
+          <t>Citrusvil</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4513,26 +4644,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Testin Cam - ROA C.Mega</t>
+          <t>Citrusvil MB</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA - CV</t>
+          <t>TRANSPORTADORA DE GAS DEL SUR S.A</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -4543,7 +4674,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SEBUN SEW</t>
+          <t>Allflex 2024 - Error de Formato - Berry</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4553,14 +4684,10 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>allfelx</t>
-        </is>
-      </c>
+          <t>GUI: Sumarización &amp; Control por Totales</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>2</v>
       </c>
@@ -4573,7 +4700,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>alflex</t>
+          <t>Testing Cam - ROA - Radio Victoria</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4588,7 +4715,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Sew Eurodrive</t>
+          <t>Allflex -MO 2</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4603,7 +4730,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tetra oven</t>
+          <t>AllCB</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4618,7 +4745,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>citrusivil_ROA</t>
+          <t>ALFEX TEST_OBS</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4633,7 +4760,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Roch - Sin macro corrida</t>
+          <t>Atanor - Sin macro corrida</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4648,7 +4775,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AllCB</t>
+          <t>Atanor ROA - Casos sin macro corrida</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4663,7 +4790,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ALFEX TEST_OBS</t>
+          <t>Allflex puma oven</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4673,12 +4800,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CO - Ultragenyx</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ULTRAGENYX</t>
+          <t>Testing  Cam - ROA Sew Eurodrive</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4688,12 +4815,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>UY - Envio Recibo de sueldos</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Allflex -MO 2</t>
+          <t>Coralnet</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4708,7 +4835,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>hsakd</t>
+          <t>Testing Cam - ROA Roch - Sin macro corrida</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4723,7 +4850,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA CV - Sin macro corrida</t>
+          <t>Testing Cam - ROA Renault - Sin macro corrida</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4738,7 +4865,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Allflex MO - Oven</t>
+          <t>Tetra oven</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4753,7 +4880,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Allflex 2024 - Error de Formato - Berry</t>
+          <t>citrusivil_ROA</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4768,7 +4895,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA C.Mega</t>
+          <t>allfelx</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4783,7 +4910,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA - Radio Victoria</t>
+          <t>Allflex MO - Oven</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4798,7 +4925,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OVEN QA - Ingredion</t>
+          <t>Testing Cam - ROA SEW - Sin macro corrida</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -4808,12 +4935,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>CO - Ultragenyx</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Allflex Oven</t>
+          <t>ULTRAGENYX</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -4828,7 +4955,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Atanor - Sin macro corrida</t>
+          <t>SEBUN SEW</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -4843,7 +4970,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Allflex puma oven</t>
+          <t>Testing Cam - ROA C.Mega</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4858,7 +4985,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Atanor ROA - Casos sin macro corrida</t>
+          <t>Testing Cam - ROA CV - Sin macro corrida</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4873,7 +5000,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cliente no especificado</t>
+          <t>Testing Cam  - ROA - CV</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4888,7 +5015,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Citrusvil ROA - Con errores</t>
+          <t>alflex</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -4903,7 +5030,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ITT MO NSSS</t>
+          <t>Testin Cam - ROA  C.Mega</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -4918,7 +5045,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ingredion nuevo ROA</t>
+          <t>Macroanexo C.Mega ROA - con errores</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -4933,7 +5060,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kodak CB</t>
+          <t>Ingredion CAN</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -4948,7 +5075,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kodak MO</t>
+          <t>ITT MO NSSS</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -4963,7 +5090,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Macroanexo C.Mega ROA - con errores</t>
+          <t>ITT MO</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -4978,7 +5105,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Citruscivil</t>
+          <t>ITT CB</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -4993,7 +5120,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Citru ROA - Oven</t>
+          <t>Kodak MO</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -5038,7 +5165,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Macroanexo ROA CV Com Errores</t>
+          <t>Copetro MO</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -5053,7 +5180,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kodak CAN</t>
+          <t>Ingredion nuevo ROA</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5068,7 +5195,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Copetro MO</t>
+          <t>Kodak CB</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5098,7 +5225,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ingredion Oven</t>
+          <t>Kodak CAN</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5113,7 +5240,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ingredion MB</t>
+          <t>Ingredion Oven</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5128,7 +5255,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ingredion CAN</t>
+          <t>Citruscivil</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5143,7 +5270,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ITT MO</t>
+          <t>OVEN QA - Ingredion</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -5158,7 +5285,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HELMERICH_CAPITAL_A_CERO</t>
+          <t>Ingredion MB</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -5173,7 +5300,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ITT CB</t>
+          <t>Citru ROA - Oven</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -5188,7 +5315,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Helmerich ROA - Casos con errores</t>
+          <t>Macroanexo ROA CV Com Errores</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -5203,7 +5330,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Helmerich MO</t>
+          <t>Sew Eurodrive ROA - con errores</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -5218,7 +5345,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>sew test</t>
+          <t>Allflex Oven</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -5233,7 +5360,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>sarasa</t>
+          <t>Cliente no especificado</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -5243,10 +5370,14 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GUI: Sumarización &amp; Control por Totales</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Citrusvil ROA - Con errores</t>
+        </is>
+      </c>
       <c r="C129" t="n">
         <v>2</v>
       </c>
@@ -5254,12 +5385,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MX - Ultragenyx</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ULTRAGENYX</t>
+          <t>HELMERICH_CAPITAL_A_CERO</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -5269,57 +5400,61 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Carga de Autonomos VEP</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TERNIUM</t>
+          <t>Helmerich ROA - Casos con errores</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Descarga de Deducciones Sufridas</t>
+          <t>NFE UY</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>TCS IBEROAMERICA S.A., TCS Solutions</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GUI: Identificación de registros faltantes</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Helmerich MO</t>
+        </is>
+      </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NFE Alert</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>COMPANIA DE INVERSIONES DE ENERGIA S.A</t>
+          <t>sarasa</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -5330,11 +5465,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>roch_roa_sass2</t>
+          <t>hsakd</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -5345,67 +5480,67 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>sasroaroasas</t>
+          <t>sew test</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>sassas</t>
+          <t>ROCHE DIABETES CARE ARGENTINA SA</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>F572</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>test 2</t>
+          <t>PRODUCTOS ROCHE S A QUIMICA E INDUSTRIAL</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>test10</t>
+          <t>30660000000000</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Carga de Autonomos VEP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>test_3</t>
+          <t>TERNIUM</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -5415,12 +5550,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>Descarga de Deducciones Sufridas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>test_33</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -5430,14 +5565,10 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>test_4</t>
-        </is>
-      </c>
+          <t>GUI: Identificación de registros faltantes</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>1</v>
       </c>
@@ -5450,7 +5581,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>test_ejecutable_consola_roa</t>
+          <t>sasroaroasas</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -5465,7 +5596,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>test_roch_ejecutable</t>
+          <t>sassas</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -5480,7 +5611,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>test_sin_c_e</t>
+          <t>ejemplo_nuevo_roa</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -5495,7 +5626,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>testing_ejecutable_xd</t>
+          <t>ejem455</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -5510,7 +5641,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>zaszas</t>
+          <t>cualquier nombre</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -5525,7 +5656,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Copetro ROA - sin macro corrida</t>
+          <t>cmega</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -5540,7 +5671,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Copetro ROA prueba amiel</t>
+          <t>citu_sss</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -5555,7 +5686,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Copetro ROA prueba eimiel</t>
+          <t>roch_roa_sass2</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -5570,7 +5701,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EMSA</t>
+          <t>roaroaroa2</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -5585,7 +5716,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EMSA ROA - Casos con errores</t>
+          <t>roacitru</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -5600,7 +5731,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMSA ROA - caso de error</t>
+          <t>roa_allflex_2</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -5615,7 +5746,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EMSA_Sin_ajuste_de_capital</t>
+          <t>prueba modd</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -5630,7 +5761,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Helmerich &amp; Payne CAN</t>
+          <t>kodak mexicana - MO - Error de formato</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -5645,7 +5776,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Helmerich &amp; Payne ROA Con Errores</t>
+          <t>ingredion3</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -5660,7 +5791,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Helmerich ROA - Caso de error</t>
+          <t>ingredion2</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -5675,7 +5806,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Helmerik ROA - Con errores</t>
+          <t>hkdahjsa</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -5690,7 +5821,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ITT - Borneman - Error de Formato - CAN</t>
+          <t>ALABS - Macro Anexo PF 2024 - Error de Instancia</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -5705,7 +5836,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ITT Berry</t>
+          <t>ALABS - MB - Errores aislados</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -5715,12 +5846,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>SygnOff</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ITT Borneman FY24 - Error de Formato - CAN</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -5735,7 +5866,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ITT MB</t>
+          <t>zaszaszaszas</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -5745,12 +5876,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE UY</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Citrusvil ROA - sin macro corrida</t>
+          <t>Tafibal, TCS IBEROAMERICA S.A., TCS Solutions</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -5760,12 +5891,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE UY</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Citrusvil_ROA_Casos con errores</t>
+          <t>Stiler S.A.</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -5780,7 +5911,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Copetro - ROA Macro Sin Correr</t>
+          <t>Copetro ROA prueba amiel</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -5795,7 +5926,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Copetro Berry</t>
+          <t>Copetro ROA - sin macro corrida</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -5810,7 +5941,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Copetro ROA - Caso de error</t>
+          <t>Copetro ROA - Sin correr macro</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -5825,7 +5956,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Copetro ROA - Casos con errores</t>
+          <t>Copetro ROA - Con errores</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -5840,7 +5971,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Copetro ROA - Con errores</t>
+          <t>Copetro ROA - Casos con errores</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -5855,7 +5986,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Copetro ROA - Sin correr macro</t>
+          <t>Helmerik ROA - Con errores</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -5870,7 +6001,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ITT ROA</t>
+          <t>Helmerich ROA - Caso de error</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -5885,7 +6016,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ITT nuevo ROA</t>
+          <t>Citrusvil_ROA_Casos con errores</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5900,7 +6031,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ITT puma oven</t>
+          <t>Citrusvil ROA - sin macro corrida</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -5915,7 +6046,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ingredion - CB - Error de formato</t>
+          <t>Citrusvil 2 - Macro sin Correr</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -5930,7 +6061,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ingredion Argentina FY 24 - Error de Formato - CB</t>
+          <t>Citrusvil - ROA Sin macro corrida</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5945,7 +6076,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ingredion Berry</t>
+          <t>EMSA</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -5960,7 +6091,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ingredion CB</t>
+          <t>Copetro ROA prueba eimiel</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -5975,7 +6106,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ingredion MO NSSS</t>
+          <t>Helmerich &amp; Payne ROA Con Errores</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -5990,7 +6121,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ingredion ROA</t>
+          <t>Helmerich &amp; Payne  CAN</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -6005,7 +6136,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>COPE</t>
+          <t>EMSA_Sin_ajuste_de_capital</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -6020,7 +6151,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>COPETRO ROA Con Errores</t>
+          <t>EMSA ROA - caso de error</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -6035,7 +6166,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Cirtusvil - Macro Sin Correr</t>
+          <t>EMSA ROA - Casos con errores</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -6050,7 +6181,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Citru sin macro</t>
+          <t>Ingredion CB</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -6065,7 +6196,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Citrusivil</t>
+          <t>Ingredion Berry</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -6080,7 +6211,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Citrusivil ROA -Sin Ajuste</t>
+          <t>Ingredion Argentina FY 24 - Error de Formato - CB</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -6095,7 +6226,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Citrusvil - ROA Sin macro corrida</t>
+          <t>Ingredion - CB - Error de formato</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -6110,7 +6241,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Citrusvil 2 - Macro sin Correr</t>
+          <t>ITT puma oven</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -6125,7 +6256,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kodak Berry</t>
+          <t>ITT nuevo ROA</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -6140,7 +6271,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Kodak MB</t>
+          <t>ITT ROA</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -6155,7 +6286,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kodak MO NSSS</t>
+          <t>ITT MB</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -6170,7 +6301,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kodak MO SSSS</t>
+          <t>ITT Borneman FY24 - Error de Formato - CAN</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -6185,7 +6316,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kodak Mexico FY24 - Error de Formato</t>
+          <t>ITT Berry</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -6200,7 +6331,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kodak Oven Testing</t>
+          <t>ITT - Borneman - Error de Formato - CAN</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -6215,7 +6346,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kodak nuevo ROA</t>
+          <t>Kodak Oven Testing</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -6230,7 +6361,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Macroanexo CV 2024 ROA Macro Sin Correr</t>
+          <t>Kodak Mexico FY24 - Error de Formato</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -6245,7 +6376,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Macroanexo ROA - sin macro corrida</t>
+          <t>Kodak MO SSSS</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -6260,7 +6391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Macroanexo ROA CV Con Errores</t>
+          <t>Kodak MO NSSS</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -6275,7 +6406,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Macroanexo ROA Con Errores</t>
+          <t>Cirtusvil - Macro Sin Correr</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -6290,7 +6421,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Macroanexo ROA ROA - SIn ajuste</t>
+          <t>COPETRO ROA Con Errores</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -6305,7 +6436,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Macroanexo sin correr - Sin correr macro</t>
+          <t>COPE</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -6320,7 +6451,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Macronexo ROA - Con errores</t>
+          <t>CITRUSVIL_ROA_SAC</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -6335,7 +6466,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Oven</t>
+          <t>CITRUSVIL ROA - Sin ajuste</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -6350,7 +6481,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Oven Tester</t>
+          <t>Borneman - Errores de formato - CAN</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -6365,7 +6496,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Probandoo</t>
+          <t>Atanor ROA - Sin macros corridas</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -6380,7 +6511,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ROA2222</t>
+          <t>Atanor ROA - Con macro corrida</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -6395,7 +6526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ROA_SAS_2</t>
+          <t>Copetro ROA - Caso de error</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -6410,7 +6541,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ROCH - Macro sin corrida</t>
+          <t>Copetro Berry</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -6425,7 +6556,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ROCH - Macroanexo ROA Macros sin Correr</t>
+          <t>Copetro - ROA Macro Sin Correr</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -6440,7 +6571,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Allflex Testing 01</t>
+          <t>Kodak MB</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -6455,7 +6586,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Allflex nuevo ROA</t>
+          <t>Kodak Berry</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -6470,7 +6601,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Allflex oven ROA</t>
+          <t>Ingredion ROA</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -6485,7 +6616,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Allflex_MO</t>
+          <t>Ingredion MO NSSS</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -6500,7 +6631,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Atanor - Macroanexo - Sin Macro Corrida</t>
+          <t>Oven Tester</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -6515,7 +6646,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Atanor ROA - Con macro corrida</t>
+          <t>Oven</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -6530,7 +6661,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Atanor ROA - Sin macros corridas</t>
+          <t>Macronexo ROA - Con errores</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -6545,7 +6676,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Borneman - Errores de formato - CAN</t>
+          <t>Macroanexo sin correr - Sin correr macro</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -6560,7 +6691,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CITRUSVIL ROA - Sin ajuste</t>
+          <t>Allflex oven ROA</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -6575,7 +6706,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CITRUSVIL_ROA_SAC</t>
+          <t>Allflex nuevo ROA</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -6590,7 +6721,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ROCH ROA - Con errores</t>
+          <t>Allflex Testing 01</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -6605,7 +6736,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>RadioVictoria ROA Con Erorres</t>
+          <t>Allflex NUM</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -6620,7 +6751,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Ratio</t>
+          <t>Allflex MO SSSN</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -6635,7 +6766,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RatioReport MATCH CODIGO ROA v3.2</t>
+          <t>Allflex MO SSNN</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -6650,7 +6781,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RatioReport MATCH CODIGO v3.2</t>
+          <t>Allflex MO SNNS</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -6665,7 +6796,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Renault - Macro sin corrida</t>
+          <t>Allflex MO SNNN</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -6680,7 +6811,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Renault - Macroanexo ROA - sin macro corrida</t>
+          <t>Allflex MO NSSS</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -6695,7 +6826,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Citrusivil ROA -Sin Ajuste</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -6710,7 +6841,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Roch ROA Con Errores</t>
+          <t>Citrusivil</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -6725,7 +6856,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>Citru sin macro</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -6740,7 +6871,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SEW - Macroanexo - Sin Macro Corrida</t>
+          <t>Macroanexo ROA Con Errores</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -6755,7 +6886,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>Macroanexo ROA CV Con Errores</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -6770,7 +6901,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SG Placo</t>
+          <t>Macroanexo ROA - sin macro corrida</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -6785,7 +6916,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SG Placo - Macro sin correr</t>
+          <t>Macroanexo ROA  ROA - SIn ajuste</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -6800,7 +6931,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SG Placo Macroanexo ROA Con Errores</t>
+          <t>Macroanexo CV 2024 ROA Macro Sin Correr</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -6815,7 +6946,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sew Eurodrive - ROA Con Errores</t>
+          <t>Kodak nuevo ROA</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -6830,7 +6961,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Sew Eurodrive ROA Con Errores 2</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -6845,7 +6976,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Test citrusvil xdxdxdx</t>
+          <t>Renault - Macroanexo ROA - sin macro corrida</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -6860,7 +6991,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Testing Cam - Ajuste capital 0</t>
+          <t>Renault - Macro sin corrida</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -6875,7 +7006,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Testing Cam - MO Allflex - Sin ajuste de Capital</t>
+          <t>RatioReport MATCH CODIGO v3.2</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -6890,7 +7021,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA</t>
+          <t>RatioReport MATCH CODIGO ROA v3.2</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -6905,7 +7036,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Atanor - Sin macro corrida</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -6920,7 +7051,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Allflex Berry</t>
+          <t>RadioVictoria ROA Con Erorres</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -6935,7 +7066,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Allflex CAN</t>
+          <t>ROCH ROA - Con errores</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -6950,7 +7081,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Allflex CAN - Oven</t>
+          <t>ROCH - Macroanexo ROA Macros sin Correr</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -6965,7 +7096,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Allflex CB</t>
+          <t>ROCH - Macro sin corrida</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -6980,7 +7111,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Allflex MO NNNS</t>
+          <t>ROA_SAS_2</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -6995,7 +7126,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Allflex MO NNSS</t>
+          <t>ROA2222</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -7010,7 +7141,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Allflex MO NSNN</t>
+          <t>Probandoo</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -7025,7 +7156,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Allflex MO NSSS</t>
+          <t>Sew Eurodrive ROA Con Errores 2</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -7040,7 +7171,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Allflex MO SNNN</t>
+          <t>Sew Eurodrive - ROA Con Errores</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -7055,7 +7186,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Allflex MO SNNS</t>
+          <t>SG Placo Macroanexo ROA Con Errores</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -7070,7 +7201,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Allflex MO SSNN</t>
+          <t>Allflex CAN - Oven</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -7085,7 +7216,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Allflex MO SSSN</t>
+          <t>Allflex CAN</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -7100,7 +7231,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Allflex NUM</t>
+          <t>Allflex Berry</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -7115,7 +7246,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Citrusvil - Sin macros corridas</t>
+          <t>Allflex - Error de formato - Berry</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -7130,7 +7261,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Copetro - Sin macro corrida</t>
+          <t>AllFlex MO SSSS</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -7145,7 +7276,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Helmerich</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -7160,7 +7291,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA Roch 2</t>
+          <t>ALFEX</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -7175,7 +7306,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA SG Placo</t>
+          <t>Atanor - Macroanexo - Sin Macro Corrida</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -7190,7 +7321,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Testing Cam - ROA SG Placo - Sin macro corrida</t>
+          <t>Allflex_MO</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -7200,12 +7331,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>NFE Alert</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Testing Cam 2</t>
+          <t>COMPANIA DE INVERSIONES DE ENERGIA S.A</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -7215,12 +7346,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+          <t>GUI: Padrones Impositivos (Nac &amp; Prov)</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Testing Cam 3</t>
+          <t>ABBVIE S.A.</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -7235,7 +7366,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Testing Cami</t>
+          <t>SG Placo - Macro sin correr</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -7250,7 +7381,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tetra FY22 - Error de Formato - MB</t>
+          <t>SG Placo</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -7265,7 +7396,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Tetra FY22 - Error de formato</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -7280,7 +7411,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Tetra MO NSSS</t>
+          <t>SEW - Macroanexo - Sin Macro Corrida</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -7295,7 +7426,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tetra MO SSSS</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -7310,7 +7441,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tetra nuevo ROA</t>
+          <t>Roch ROA Con Errores</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -7325,7 +7456,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>allflex2</t>
+          <t>Testing Cam - ROA Copetro - Sin macro corrida</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -7340,7 +7471,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>asasasasasasasasasasDIGO</t>
+          <t>Testing Cam - ROA Citrusvil  - Sin macros corridas</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -7355,7 +7486,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>citrsvil_roa</t>
+          <t>Testing Cam - ROA Atanor - Sin macro corrida</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -7370,7 +7501,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>citrusivil - sac</t>
+          <t>Testing Cam - ROA  SG Placo - Sin macro corrida</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -7385,7 +7516,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>citrusivil -ca0</t>
+          <t>Testing Cam - ROA</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -7400,7 +7531,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>citrusivil_casos_con_errores_roa</t>
+          <t>Testing Cam - MO Allflex - Sin ajuste de Capital</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -7415,7 +7546,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>citrusivil_roa_casos_con_errores</t>
+          <t>Testing Cam - Ajuste capital 0</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -7430,7 +7561,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ALABS - MB - Errores aislados</t>
+          <t>Testing  Cam - ROA SG Placo</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -7445,7 +7576,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>ALABS - Macro Anexo PF 2024 - Error de Instancia</t>
+          <t>Test citrusvil xdxdxdx</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -7460,7 +7591,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ALFEX</t>
+          <t>Tetra nuevo ROA</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -7475,7 +7606,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tetra MO SSSS</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -7490,7 +7621,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AllFlex MO SSSS</t>
+          <t>Tetra MO NSSS</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -7505,7 +7636,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Allflex - Error de formato - Berry</t>
+          <t>citrusvil ROA Caso con errores</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -7535,7 +7666,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>citrusvil ROA Caso con errores</t>
+          <t>citrusivil_roa_casos_con_errores</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -7550,7 +7681,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>citu_sss</t>
+          <t>citrusivil_casos_con_errores_roa</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -7565,7 +7696,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>cmega</t>
+          <t>citrusivil -ca0</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -7580,7 +7711,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>cualquier nombre</t>
+          <t>citrusivil - sac</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7595,7 +7726,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>ejem455</t>
+          <t>citrsvil_roa</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7610,7 +7741,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>ejemplo_nuevo_roa</t>
+          <t>asasasasasasasasasasDIGO</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7625,7 +7756,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>hkdahjsa</t>
+          <t>allflex2</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -7640,7 +7771,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ingredion2</t>
+          <t>Allflex MO NSNN</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7655,7 +7786,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ingredion3</t>
+          <t>Allflex MO NNSS</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7670,7 +7801,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>kodak mexicana - MO - Error de formato</t>
+          <t>Allflex MO NNNS</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -7685,7 +7816,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>prueba modd</t>
+          <t>Allflex CB</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -7700,7 +7831,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>roa_allflex_2</t>
+          <t>Tetra FY22 - Error de formato</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -7715,7 +7846,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>roacitru</t>
+          <t>Tetra FY22 - Error de Formato - MB</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -7730,7 +7861,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>roaroaroa2</t>
+          <t>Testing Cami</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -7745,7 +7876,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>zaszaszas</t>
+          <t>Testing Cam 3</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -7760,7 +7891,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>zaszaszaszas</t>
+          <t>Testing Cam 2</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -7770,12 +7901,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Tracking de Vencimientos</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BINTI ABDUL RASHID, NURUL SHAKILA</t>
+          <t>Testing Cam - ROA Roch 2</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -7785,12 +7916,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Tracking de Vencimientos</t>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BINTI UMAR FAIZ DANIEL, NOUR INAYA DELAILA</t>
+          <t>Testing Cam - ROA Helmerich</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -7800,15 +7931,225 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>test 2</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Tracking de Vencimientos</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>BINTI UMAR FAIZ DANIEL, NOUR INAYA DELAILA</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Tracking de Vencimientos</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>BINTI ABDUL RASHID, NURUL SHAKILA</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Tracking de Vencimientos</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>AGUERO VINDAS, CRISTIN NICOLE</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>zaszaszas</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>zaszas</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>testing_ejecutable_xd</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>test_sin_c_e</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>test_roch_ejecutable</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>test_ejecutable_consola_roa</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>test_4</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>test_33</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>test_3</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Tablas Ratio Report para informes de Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>test10</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
           <t>Carga de Autonomos VEP</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>TENARIS</t>
         </is>
       </c>
-      <c r="C300" t="n">
+      <c r="C314" t="n">
         <v>1</v>
       </c>
     </row>
